--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488302_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488302_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.394500000000001</v>
+        <v>7.24</v>
       </c>
       <c r="E2" t="n">
-        <v>6.3033</v>
+        <v>5.8137</v>
       </c>
       <c r="F2" t="n">
-        <v>2.0912</v>
+        <v>1.4264</v>
       </c>
       <c r="G2" t="n">
         <v>5.1945</v>
@@ -610,13 +610,13 @@
         <v>2.7793</v>
       </c>
       <c r="S2" t="n">
-        <v>1.6447</v>
+        <v>0.4903</v>
       </c>
       <c r="T2" t="n">
-        <v>0.5397</v>
+        <v>0.0501</v>
       </c>
       <c r="U2" t="n">
-        <v>1.105</v>
+        <v>0.4402</v>
       </c>
       <c r="V2" t="n">
         <v>0.6289</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.2413</v>
+        <v>6.7129</v>
       </c>
       <c r="E3" t="n">
-        <v>6.3881</v>
+        <v>6.7366</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.1468</v>
+        <v>-0.0237</v>
       </c>
       <c r="G3" t="n">
         <v>5.8648</v>
@@ -688,13 +688,13 @@
         <v>2.0382</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.0508</v>
+        <v>-0.5792</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.766</v>
+        <v>-0.4175</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2848</v>
+        <v>-0.1617</v>
       </c>
       <c r="V3" t="n">
         <v>0.3155</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>5.6917</v>
+        <v>5.3223</v>
       </c>
       <c r="E4" t="n">
         <v>2.6174</v>
       </c>
       <c r="F4" t="n">
-        <v>3.0743</v>
+        <v>2.7049</v>
       </c>
       <c r="G4" t="n">
         <v>2.4519</v>
@@ -766,13 +766,13 @@
         <v>2.0382</v>
       </c>
       <c r="S4" t="n">
-        <v>0.8692</v>
+        <v>0.4999</v>
       </c>
       <c r="T4" t="n">
         <v>-0.0037</v>
       </c>
       <c r="U4" t="n">
-        <v>0.8729</v>
+        <v>0.5036</v>
       </c>
       <c r="V4" t="n">
         <v>1.2589</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.5878</v>
+        <v>3.323</v>
       </c>
       <c r="E5" t="n">
-        <v>3.6301</v>
+        <v>3.5869</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.0423</v>
+        <v>-0.2639</v>
       </c>
       <c r="G5" t="n">
         <v>0.3181</v>
@@ -844,13 +844,13 @@
         <v>1.1117</v>
       </c>
       <c r="S5" t="n">
-        <v>0.5847</v>
+        <v>0.3199</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1604</v>
+        <v>0.1172</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4243</v>
+        <v>0.2027</v>
       </c>
       <c r="V5" t="n">
         <v>1.5733</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. RODRIGUEZ LEIRO</t>
+          <t>P. OSES BERNALDEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3.4966</v>
+        <v>3.2365</v>
       </c>
       <c r="E6" t="n">
-        <v>5.1256</v>
+        <v>2.5536</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.629</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="G6" t="n">
-        <v>1.8852</v>
+        <v>0.1376</v>
       </c>
       <c r="H6" t="n">
-        <v>3.4656</v>
+        <v>-0.2356</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.5804</v>
+        <v>0.3732</v>
       </c>
       <c r="J6" t="n">
-        <v>4.2167</v>
+        <v>0.9491000000000001</v>
       </c>
       <c r="K6" t="n">
-        <v>4.0923</v>
+        <v>0.2228</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1244</v>
+        <v>0.7264</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.3315</v>
+        <v>-0.8115</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.6267</v>
+        <v>-0.4584</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.7048</v>
+        <v>-0.3531</v>
       </c>
       <c r="P6" t="n">
-        <v>0.9264</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-1.8529</v>
       </c>
       <c r="R6" t="n">
-        <v>0.9264</v>
+        <v>1.8529</v>
       </c>
       <c r="S6" t="n">
-        <v>0.6849</v>
+        <v>0.2674</v>
       </c>
       <c r="T6" t="n">
-        <v>0.5944</v>
+        <v>-0.0037</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0905</v>
+        <v>0.2711</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>2.8316</v>
       </c>
       <c r="W6" t="n">
-        <v>0.3144</v>
+        <v>3.461</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.3144</v>
+        <v>-0.6294</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>P. OSES BERNALDEZ</t>
+          <t>A. RODRIGUEZ LEIRO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>3.0888</v>
+        <v>3.1601</v>
       </c>
       <c r="E7" t="n">
-        <v>2.5536</v>
+        <v>4.6906</v>
       </c>
       <c r="F7" t="n">
-        <v>0.5352</v>
+        <v>-1.5305</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1376</v>
+        <v>1.8852</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.2356</v>
+        <v>3.4656</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3732</v>
+        <v>-1.5804</v>
       </c>
       <c r="J7" t="n">
-        <v>0.9491000000000001</v>
+        <v>4.2167</v>
       </c>
       <c r="K7" t="n">
-        <v>0.2228</v>
+        <v>4.0923</v>
       </c>
       <c r="L7" t="n">
-        <v>0.7264</v>
+        <v>0.1244</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.8115</v>
+        <v>-2.3315</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.4584</v>
+        <v>-0.6267</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.3531</v>
+        <v>-1.7048</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>0.9264</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.8529</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.8529</v>
+        <v>0.9264</v>
       </c>
       <c r="S7" t="n">
-        <v>0.1196</v>
+        <v>0.3485</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.0037</v>
+        <v>0.1595</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1233</v>
+        <v>0.189</v>
       </c>
       <c r="V7" t="n">
-        <v>2.8316</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>3.461</v>
+        <v>0.3144</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.6294</v>
+        <v>-0.3144</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.6098</v>
+        <v>2.7385</v>
       </c>
       <c r="E8" t="n">
-        <v>0.243</v>
+        <v>0.9285</v>
       </c>
       <c r="F8" t="n">
-        <v>1.3668</v>
+        <v>1.81</v>
       </c>
       <c r="G8" t="n">
         <v>0.1745</v>
@@ -1078,13 +1078,13 @@
         <v>1.6676</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.8623</v>
+        <v>0.2664</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.766</v>
+        <v>-0.0805</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0963</v>
+        <v>0.3469</v>
       </c>
       <c r="V8" t="n">
         <v>0.63</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.7292</v>
+        <v>0.9245</v>
       </c>
       <c r="E10" t="n">
-        <v>1.3685</v>
+        <v>1.6623</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.6394</v>
+        <v>-0.7378</v>
       </c>
       <c r="G10" t="n">
         <v>0.3213</v>
@@ -1234,13 +1234,13 @@
         <v>1.4823</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.4449</v>
+        <v>-0.2496</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5471</v>
+        <v>-0.2534</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1022</v>
+        <v>0.0037</v>
       </c>
       <c r="V10" t="n">
         <v>-0.6294</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. MENDEZ CARRION</t>
+          <t>A. CUADRA CRESPO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.1738</v>
+        <v>-0.1646</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.4234</v>
+        <v>0.5436</v>
       </c>
       <c r="F11" t="n">
-        <v>1.2497</v>
+        <v>-0.7082000000000001</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.2423</v>
+        <v>-0.5383</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.9981</v>
+        <v>1.1038</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.2441</v>
+        <v>-1.642</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.5292</v>
+        <v>0.5666</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.8763</v>
+        <v>1.095</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.6529</v>
+        <v>-0.5284</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.7131</v>
+        <v>-1.1048</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.1219</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.5913</v>
+        <v>-1.1136</v>
       </c>
       <c r="P11" t="n">
-        <v>0.7411</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0.7411</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="S11" t="n">
-        <v>0.6974</v>
+        <v>-0.1822</v>
       </c>
       <c r="T11" t="n">
-        <v>0.1057</v>
+        <v>-0.023</v>
       </c>
       <c r="U11" t="n">
-        <v>0.5917</v>
+        <v>-0.1592</v>
       </c>
       <c r="V11" t="n">
-        <v>0.63</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>0.63</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A. CUADRA CRESPO</t>
+          <t>A. MENDEZ CARRION</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.3358</v>
+        <v>-0.4627</v>
       </c>
       <c r="E12" t="n">
-        <v>0.3477</v>
+        <v>-1.5646</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.6835</v>
+        <v>1.1019</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.5383</v>
+        <v>-2.2423</v>
       </c>
       <c r="H12" t="n">
-        <v>1.1038</v>
+        <v>-0.9981</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.642</v>
+        <v>-1.2441</v>
       </c>
       <c r="J12" t="n">
-        <v>0.5666</v>
+        <v>-1.5292</v>
       </c>
       <c r="K12" t="n">
-        <v>1.095</v>
+        <v>-0.8763</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.5284</v>
+        <v>-0.6529</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.1048</v>
+        <v>-0.7131</v>
       </c>
       <c r="N12" t="n">
-        <v>0.008699999999999999</v>
+        <v>-0.1219</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.1136</v>
+        <v>-0.5913</v>
       </c>
       <c r="P12" t="n">
-        <v>0.5558999999999999</v>
+        <v>0.7411</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>0.5558999999999999</v>
+        <v>0.7411</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.3534</v>
+        <v>0.4085</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.2189</v>
+        <v>-0.0354</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1346</v>
+        <v>0.4439</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>0.63</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.0251</v>
+        <v>-1.803</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.8063</v>
+        <v>-1.9042</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.2188</v>
+        <v>0.1012</v>
       </c>
       <c r="G13" t="n">
         <v>-3.0798</v>
@@ -1468,13 +1468,13 @@
         <v>2.2234</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.2243</v>
+        <v>-0.0022</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.0584</v>
+        <v>-0.1564</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.1659</v>
+        <v>0.1542</v>
       </c>
       <c r="V13" t="n">
         <v>-0.9444</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-5.1781</v>
+        <v>-4.8274</v>
       </c>
       <c r="E14" t="n">
-        <v>-3.4839</v>
+        <v>-3.5272</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.6942</v>
+        <v>-1.3002</v>
       </c>
       <c r="G14" t="n">
         <v>-5.9929</v>
@@ -1546,13 +1546,13 @@
         <v>1.1117</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.2969</v>
+        <v>0.0538</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.1679</v>
+        <v>-0.2111</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.1291</v>
+        <v>0.2649</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>26.7152</v>
+        <v>26.9884</v>
       </c>
       <c r="E15" t="n">
-        <v>23.452</v>
+        <v>23.7255</v>
       </c>
       <c r="F15" t="n">
-        <v>3.2632</v>
+        <v>3.2631</v>
       </c>
       <c r="G15" t="n">
         <v>6.0829</v>
@@ -1624,13 +1624,13 @@
         <v>18.5287</v>
       </c>
       <c r="S15" t="n">
-        <v>1.3679</v>
+        <v>1.6415</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.1315</v>
+        <v>-0.8579000000000001</v>
       </c>
       <c r="U15" t="n">
-        <v>2.4992</v>
+        <v>2.4993</v>
       </c>
       <c r="V15" t="n">
         <v>6.294399999999999</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.2175</v>
+        <v>4.2236</v>
       </c>
       <c r="E16" t="n">
-        <v>5.1872</v>
+        <v>5.7748</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.9698</v>
+        <v>-1.5512</v>
       </c>
       <c r="G16" t="n">
         <v>3.6879</v>
@@ -1702,13 +1702,13 @@
         <v>0.5558999999999999</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.3587</v>
+        <v>-0.3525</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.3132</v>
+        <v>-0.7256</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0455</v>
+        <v>0.373</v>
       </c>
       <c r="V16" t="n">
         <v>1.2589</v>
@@ -1735,10 +1735,10 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.8202</v>
+        <v>1.3305</v>
       </c>
       <c r="E17" t="n">
-        <v>3.8763</v>
+        <v>3.3866</v>
       </c>
       <c r="F17" t="n">
         <v>-2.0561</v>
@@ -1780,10 +1780,10 @@
         <v>0.7411</v>
       </c>
       <c r="S17" t="n">
-        <v>1.1751</v>
+        <v>0.6855</v>
       </c>
       <c r="T17" t="n">
-        <v>0.7586000000000001</v>
+        <v>0.2689</v>
       </c>
       <c r="U17" t="n">
         <v>0.4166</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1359</v>
+        <v>-0.9676</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.585</v>
+        <v>-1.3684</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7209</v>
+        <v>0.4008</v>
       </c>
       <c r="G18" t="n">
         <v>0.8366</v>
@@ -1858,13 +1858,13 @@
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>1.4666</v>
+        <v>0.3631</v>
       </c>
       <c r="T18" t="n">
-        <v>0.6491</v>
+        <v>-0.1343</v>
       </c>
       <c r="U18" t="n">
-        <v>0.8175</v>
+        <v>0.4974</v>
       </c>
       <c r="V18" t="n">
         <v>-0.3144</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.0747</v>
+        <v>-1.1475</v>
       </c>
       <c r="E19" t="n">
-        <v>1.1552</v>
+        <v>0.9594</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.2299</v>
+        <v>-2.1068</v>
       </c>
       <c r="G19" t="n">
         <v>-0.1666</v>
@@ -1936,13 +1936,13 @@
         <v>0.3706</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.6504</v>
+        <v>-0.7231</v>
       </c>
       <c r="T19" t="n">
-        <v>0.051</v>
+        <v>-0.1449</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.7014</v>
+        <v>-0.5783</v>
       </c>
       <c r="V19" t="n">
         <v>-0.6283</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.0747</v>
+        <v>-2.8548</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.8379</v>
+        <v>-2.5441</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.2368</v>
+        <v>-0.3107</v>
       </c>
       <c r="G20" t="n">
         <v>-0.5547</v>
@@ -2014,13 +2014,13 @@
         <v>0.1853</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.538</v>
+        <v>-0.318</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.7113</v>
+        <v>-0.4175</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1733</v>
+        <v>0.09950000000000001</v>
       </c>
       <c r="V20" t="n">
         <v>-0.3144</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.2535</v>
+        <v>-3.2294</v>
       </c>
       <c r="E21" t="n">
-        <v>0.2835</v>
+        <v>0.3814</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.5369</v>
+        <v>-3.6108</v>
       </c>
       <c r="G21" t="n">
         <v>1.5742</v>
@@ -2092,13 +2092,13 @@
         <v>0.5558999999999999</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.104</v>
+        <v>-0.0799</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.4961</v>
+        <v>-0.3982</v>
       </c>
       <c r="U21" t="n">
-        <v>0.3922</v>
+        <v>0.3183</v>
       </c>
       <c r="V21" t="n">
         <v>-1.5738</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.2835</v>
+        <v>-3.504</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.3498</v>
+        <v>-1.5457</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.9337</v>
+        <v>-1.9583</v>
       </c>
       <c r="G22" t="n">
         <v>-2.6597</v>
@@ -2170,13 +2170,13 @@
         <v>0.7411</v>
       </c>
       <c r="S22" t="n">
-        <v>0.5059</v>
+        <v>0.2854</v>
       </c>
       <c r="T22" t="n">
-        <v>0.1057</v>
+        <v>-0.0901</v>
       </c>
       <c r="U22" t="n">
-        <v>0.4002</v>
+        <v>0.3755</v>
       </c>
       <c r="V22" t="n">
         <v>-0.9444</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.6326</v>
+        <v>-3.6807</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.0943</v>
+        <v>-2.2901</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.5383</v>
+        <v>-1.3906</v>
       </c>
       <c r="G23" t="n">
         <v>-1.4414</v>
@@ -2248,13 +2248,13 @@
         <v>0.5558999999999999</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.5792</v>
+        <v>-0.6274</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.2226</v>
+        <v>-0.4184</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.3567</v>
+        <v>-0.2089</v>
       </c>
       <c r="V23" t="n">
         <v>-0.315</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.5935</v>
+        <v>-4.2499</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.1707</v>
+        <v>-0.9748</v>
       </c>
       <c r="F24" t="n">
-        <v>-3.4228</v>
+        <v>-3.2751</v>
       </c>
       <c r="G24" t="n">
         <v>-2.5131</v>
@@ -2326,13 +2326,13 @@
         <v>0.5558999999999999</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.1539</v>
+        <v>0.1896</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.2773</v>
+        <v>-0.0814</v>
       </c>
       <c r="U24" t="n">
-        <v>0.1233</v>
+        <v>0.2711</v>
       </c>
       <c r="V24" t="n">
         <v>-0.6294</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-5.2186</v>
+        <v>-4.9024</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.6497</v>
+        <v>-1.9642</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.5689</v>
+        <v>-2.9382</v>
       </c>
       <c r="G25" t="n">
         <v>-1.3638</v>
@@ -2404,13 +2404,13 @@
         <v>0.9264</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.7436</v>
+        <v>-0.4275</v>
       </c>
       <c r="T25" t="n">
-        <v>-1.149</v>
+        <v>-0.4635</v>
       </c>
       <c r="U25" t="n">
-        <v>0.4054</v>
+        <v>0.036</v>
       </c>
       <c r="V25" t="n">
         <v>-1.2583</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-7.7577</v>
+        <v>-7.733</v>
       </c>
       <c r="E26" t="n">
         <v>-3.078</v>
       </c>
       <c r="F26" t="n">
-        <v>-4.6797</v>
+        <v>-4.6551</v>
       </c>
       <c r="G26" t="n">
         <v>-1.8135</v>
@@ -2482,13 +2482,13 @@
         <v>0.3706</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.3877</v>
+        <v>-0.3631</v>
       </c>
       <c r="T26" t="n">
         <v>0.1057</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.4934</v>
+        <v>-0.4688</v>
       </c>
       <c r="V26" t="n">
         <v>-3.1477</v>
@@ -2518,10 +2518,10 @@
         <v>-26.7152</v>
       </c>
       <c r="E27" t="n">
-        <v>-3.263200000000001</v>
+        <v>-3.2631</v>
       </c>
       <c r="F27" t="n">
-        <v>-23.452</v>
+        <v>-23.4521</v>
       </c>
       <c r="G27" t="n">
         <v>-6.083</v>
@@ -2563,10 +2563,10 @@
         <v>-1.3679</v>
       </c>
       <c r="T27" t="n">
-        <v>-2.4994</v>
+        <v>-2.499299999999999</v>
       </c>
       <c r="U27" t="n">
-        <v>1.1315</v>
+        <v>1.1314</v>
       </c>
       <c r="V27" t="n">
         <v>-6.2941</v>
